--- a/tests/test_results.xlsx
+++ b/tests/test_results.xlsx
@@ -579,11 +579,11 @@
         <v>200</v>
       </c>
       <c r="L2" t="n">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"token": "eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJpZCI6ImNtcnN5cmk1YjAwMDBsY2I0Z2hzd2I4ZTUiLCJ1c2VybmFtZSI6ImFkbWluIiwicm9sZSI6IlNVUEVSQURNSU4iLCJpYXQiOjE3ODQ3MDI0MjIsImV4cC</t>
+          <t>{"success": true, "data": {"token": "eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJpZCI6ImNtcnN5cmk1YjAwMDBsY2I0Z2hzd2I4ZTUiLCJ1c2VybmFtZSI6ImFkbWluIiwicm9sZSI6IlNVUEVSQURNSU4iLCJpYXQiOjE3ODQ3MDMxMTcsImV4cC</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         <v>401</v>
       </c>
       <c r="L3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         <v>200</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>200</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>200</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -872,11 +872,11 @@
         <v>201</v>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvpqqtg002dlcsgf9xeymmm", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10, "createdAt":</t>
+          <t>{"success": true, "data": {"id": "cmrvq5mwi002wlcsgjrf5f2io", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10, "createdAt":</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{"eventId": "cmrvgy4ej0000lcg4jjl9dux1", "fullName": "Excel Tester Guest", "email": "excel.test.1784702422863@example.com", "phone": "0899999999", "company": "Excel QA Corp"}</t>
+          <t>{"eventId": "cmrvgy4ej0000lcg4jjl9dux1", "fullName": "Excel Tester Guest", "email": "excel.test.1784703117635@example.com", "phone": "0899999999", "company": "Excel QA Corp"}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -933,11 +933,11 @@
         <v>201</v>
       </c>
       <c r="L8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvpqqu8002glcsgnhupmmi0", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "fullName": "Excel Tester Guest", "email": "excel.test.1784702422863@example.com", "phone": "08999</t>
+          <t>{"success": true, "data": {"id": "cmrvq5mxk002zlcsgxmff7f50", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "fullName": "Excel Tester Guest", "email": "excel.test.1784703117635@example.com", "phone": "08999</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"registrationId": "cmrvpqqu8002glcsgnhupmmi0", "checkinPointId": "cmrvpqqtg002dlcsgf9xeymmm", "method": "MANUAL"}</t>
+          <t>{"registrationId": "cmrvq5mxk002zlcsgxmff7f50", "checkinPointId": "cmrvq5mwi002wlcsgjrf5f2io", "method": "MANUAL"}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -994,11 +994,11 @@
         <v>201</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"checkin": {"id": "cmrvpqquw002jlcsgdmarwb6d", "registrationId": "cmrvpqqu8002glcsgnhupmmi0", "checkinPointId": "cmrvpqqtg002dlcsgf9xeymmm", "checkinTime": "2026-07-22T06:40</t>
+          <t>{"success": true, "data": {"checkin": {"id": "cmrvq5myj0032lcsg68wwjoe8", "registrationId": "cmrvq5mxk002zlcsgxmff7f50", "checkinPointId": "cmrvq5mwi002wlcsgjrf5f2io", "checkinTime": "2026-07-22T06:51</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
         <v>200</v>
       </c>
       <c r="L10" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1112,11 +1112,11 @@
         <v>201</v>
       </c>
       <c r="L11" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvpqqvx002mlcsgtvnoje3u", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "prizeId": "cmrvgy4fj000alcg4qurjil4y", "status": "PENDING", "drawCount": 1, "startedAt": null, "e</t>
+          <t>{"success": true, "data": {"id": "cmrvq5n0p0035lcsgnmglun7w", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "prizeId": "cmrvgy4fj000alcg4qurjil4y", "status": "PENDING", "drawCount": 1, "startedAt": null, "e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>/api/draws/cmrvpqqvx002mlcsgtvnoje3u/spin</t>
+          <t>/api/draws/cmrvq5n0p0035lcsgnmglun7w/spin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1173,11 +1173,11 @@
         <v>200</v>
       </c>
       <c r="L12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"winners": [{"id": "cmrvmonyq000mlcsg5pd907ed", "fullName": "Automation Test Guest", "department": "Software Testing", "company": "Antigravity QA Labs", "employeeType": null</t>
+          <t>{"success": true, "data": {"winners": [{"id": "cmrvq5mxk002zlcsgxmff7f50", "fullName": "Excel Tester Guest", "department": null, "company": "Excel QA Corp", "employeeType": null}], "candidates": 36}}</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>/api/draws/winners/cmrvpqqx1002plcsg6vok78t3</t>
+          <t>/api/draws/winners/cmrvq5n2a0038lcsgnafwcxsn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1234,11 +1234,11 @@
         <v>200</v>
       </c>
       <c r="L13" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvpqqx1002plcsg6vok78t3", "drawSessionId": "cmrvpqqvx002mlcsgtvnoje3u", "registrationId": "cmrvmonyq000mlcsg5pd907ed", "prizeId": "cmrvgy4fj000alcg4qurjil4y", "stat</t>
+          <t>{"success": true, "data": {"id": "cmrvq5n2a0038lcsgnafwcxsn", "drawSessionId": "cmrvq5n0p0035lcsgnmglun7w", "registrationId": "cmrvq5mxk002zlcsgxmff7f50", "prizeId": "cmrvgy4fj000alcg4qurjil4y", "stat</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>/api/draws/winners/cmrvpqqx1002plcsg6vok78t3</t>
+          <t>/api/draws/winners/cmrvq5n2a0038lcsgnafwcxsn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
         <v>200</v>
       </c>
       <c r="L14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>

--- a/tests/test_results.xlsx
+++ b/tests/test_results.xlsx
@@ -579,11 +579,11 @@
         <v>200</v>
       </c>
       <c r="L2" t="n">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"token": "eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJpZCI6ImNtcnN5cmk1YjAwMDBsY2I0Z2hzd2I4ZTUiLCJ1c2VybmFtZSI6ImFkbWluIiwicm9sZSI6IlNVUEVSQURNSU4iLCJpYXQiOjE3ODQ3MDMxMTcsImV4cC</t>
+          <t>{"success": true, "data": {"token": "eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJpZCI6ImNtcnN5cmk1YjAwMDBsY2I0Z2hzd2I4ZTUiLCJ1c2VybmFtZSI6ImFkbWluIiwicm9sZSI6IlNVUEVSQURNSU4iLCJpYXQiOjE3ODQ3MDM3OTQsImV4cC</t>
         </is>
       </c>
     </row>
@@ -697,11 +697,11 @@
         <v>200</v>
       </c>
       <c r="L4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"success": true, "data": [{"id": "cmrvgy4ej0000lcg4jjl9dux1", "name": "Tech Conference 2026", "description": "Annual technology conference with workshops, talks, and networking", "venue": "Bangkok Co</t>
+          <t>{"success": true, "data": [{"id": "cmrvqjvqm0000lcswueuniggq", "name": "Tech Conference 2026", "description": "Annual technology conference with workshops, talks, and networking", "venue": "Bangkok Co</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>/api/events/cmrvgy4ej0000lcg4jjl9dux1</t>
+          <t>/api/events/cmrvqjvqm0000lcswueuniggq</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -754,11 +754,11 @@
         <v>200</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvgy4ej0000lcg4jjl9dux1", "name": "Tech Conference 2026", "description": "Annual technology conference with workshops, talks, and networking", "venue": "Bangkok Con</t>
+          <t>{"success": true, "data": {"id": "cmrvqjvqm0000lcswueuniggq", "name": "Tech Conference 2026", "description": "Annual technology conference with workshops, talks, and networking", "venue": "Bangkok Con</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>/api/checkin/points?eventId=cmrvgy4ej0000lcg4jjl9dux1</t>
+          <t>/api/checkin/points?eventId=cmrvqjvqm0000lcswueuniggq</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -811,11 +811,11 @@
         <v>200</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"success": true, "data": [{"id": "cmrvgy4eq0002lcg4dhxbk1yn", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "name": "Main Entrance", "location": "Hall A - Ground Floor", "isActive": true, "sortOrder": 1, "</t>
+          <t>{"success": true, "data": [{"id": "cmrvqjvqu0002lcswyyqtzxlt", "eventId": "cmrvqjvqm0000lcswueuniggq", "name": "Main Entrance", "location": "Hall A - Ground Floor", "isActive": true, "sortOrder": 1, "</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{"eventId": "cmrvgy4ej0000lcg4jjl9dux1", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10}</t>
+          <t>{"eventId": "cmrvqjvqm0000lcswueuniggq", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -872,11 +872,11 @@
         <v>201</v>
       </c>
       <c r="L7" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvq5mwi002wlcsgjrf5f2io", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10, "createdAt":</t>
+          <t>{"success": true, "data": {"id": "cmrvqk5le003xlcsgrrbkgwz6", "eventId": "cmrvqjvqm0000lcswueuniggq", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10, "createdAt":</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{"eventId": "cmrvgy4ej0000lcg4jjl9dux1", "fullName": "Excel Tester Guest", "email": "excel.test.1784703117635@example.com", "phone": "0899999999", "company": "Excel QA Corp"}</t>
+          <t>{"eventId": "cmrvqjvqm0000lcswueuniggq", "fullName": "Excel Tester Guest", "email": "excel.test.1784703795082@example.com", "phone": "0899999999", "company": "Excel QA Corp"}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -933,11 +933,11 @@
         <v>201</v>
       </c>
       <c r="L8" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvq5mxk002zlcsgxmff7f50", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "fullName": "Excel Tester Guest", "email": "excel.test.1784703117635@example.com", "phone": "08999</t>
+          <t>{"success": true, "data": {"id": "cmrvqk5nl0040lcsgl5jz45qp", "eventId": "cmrvqjvqm0000lcswueuniggq", "fullName": "Excel Tester Guest", "email": "excel.test.1784703795082@example.com", "phone": "08999</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"registrationId": "cmrvq5mxk002zlcsgxmff7f50", "checkinPointId": "cmrvq5mwi002wlcsgjrf5f2io", "method": "MANUAL"}</t>
+          <t>{"registrationId": "cmrvqk5nl0040lcsgl5jz45qp", "checkinPointId": "cmrvqk5le003xlcsgrrbkgwz6", "method": "MANUAL"}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -994,11 +994,11 @@
         <v>201</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"checkin": {"id": "cmrvq5myj0032lcsg68wwjoe8", "registrationId": "cmrvq5mxk002zlcsgxmff7f50", "checkinPointId": "cmrvq5mwi002wlcsgjrf5f2io", "checkinTime": "2026-07-22T06:51</t>
+          <t>{"success": true, "data": {"checkin": {"id": "cmrvqk5q20043lcsg0mi1ao5o", "registrationId": "cmrvqk5nl0040lcsgl5jz45qp", "checkinPointId": "cmrvqk5le003xlcsgrrbkgwz6", "checkinTime": "2026-07-22T07:03</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>/api/prizes?eventId=cmrvgy4ej0000lcg4jjl9dux1</t>
+          <t>/api/prizes?eventId=cmrvqjvqm0000lcswueuniggq</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1051,11 +1051,11 @@
         <v>200</v>
       </c>
       <c r="L10" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"success": true, "data": [{"id": "cmrvgy4fj000clcg4p4ok73xt", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "name": "MacBook Pro 16\"", "description": "Apple MacBook Pro 16-inch M4 Pro", "image": null, "qu</t>
+          <t>{"success": true, "data": [{"id": "cmrvqjvrn000alcsw216ijgbl", "eventId": "cmrvqjvqm0000lcswueuniggq", "name": "MacBook Pro 16\"", "description": "Apple MacBook Pro 16-inch M4 Pro", "image": null, "qu</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{"eventId": "cmrvgy4ej0000lcg4jjl9dux1", "prizeId": "cmrvgy4fj000alcg4qurjil4y", "drawCount": 1}</t>
+          <t>{"eventId": "cmrvqjvqm0000lcswueuniggq", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "drawCount": 1}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1112,11 +1112,11 @@
         <v>201</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvq5n0p0035lcsgnmglun7w", "eventId": "cmrvgy4ej0000lcg4jjl9dux1", "prizeId": "cmrvgy4fj000alcg4qurjil4y", "status": "PENDING", "drawCount": 1, "startedAt": null, "e</t>
+          <t>{"success": true, "data": {"id": "cmrvqk5t90046lcsgtf7uoplm", "eventId": "cmrvqjvqm0000lcswueuniggq", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "status": "PENDING", "drawCount": 1, "startedAt": null, "e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>/api/draws/cmrvq5n0p0035lcsgnmglun7w/spin</t>
+          <t>/api/draws/cmrvqk5t90046lcsgtf7uoplm/spin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1173,11 +1173,11 @@
         <v>200</v>
       </c>
       <c r="L12" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"winners": [{"id": "cmrvq5mxk002zlcsgxmff7f50", "fullName": "Excel Tester Guest", "department": null, "company": "Excel QA Corp", "employeeType": null}], "candidates": 36}}</t>
+          <t>{"success": true, "data": {"winners": [{"id": "cmrvqjvx70020lcsw64qrgb8g", "fullName": "Attendee 029", "department": "Finance", "company": "Tech Corp", "employeeType": "Contract"}], "candidates": 31}}</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>/api/draws/winners/cmrvq5n2a0038lcsgnafwcxsn</t>
+          <t>/api/draws/winners/cmrvqk5vb0049lcsg5y5vtfki</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1234,11 +1234,11 @@
         <v>200</v>
       </c>
       <c r="L13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvq5n2a0038lcsgnafwcxsn", "drawSessionId": "cmrvq5n0p0035lcsgnmglun7w", "registrationId": "cmrvq5mxk002zlcsgxmff7f50", "prizeId": "cmrvgy4fj000alcg4qurjil4y", "stat</t>
+          <t>{"success": true, "data": {"id": "cmrvqk5vb0049lcsg5y5vtfki", "drawSessionId": "cmrvqk5t90046lcsgtf7uoplm", "registrationId": "cmrvqjvx70020lcsw64qrgb8g", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "stat</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>/api/draws/winners/cmrvq5n2a0038lcsgnafwcxsn</t>
+          <t>/api/draws/winners/cmrvqk5vb0049lcsg5y5vtfki</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>

--- a/tests/test_results.xlsx
+++ b/tests/test_results.xlsx
@@ -442,7 +442,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -579,11 +579,11 @@
         <v>200</v>
       </c>
       <c r="L2" t="n">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"token": "eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJpZCI6ImNtcnN5cmk1YjAwMDBsY2I0Z2hzd2I4ZTUiLCJ1c2VybmFtZSI6ImFkbWluIiwicm9sZSI6IlNVUEVSQURNSU4iLCJpYXQiOjE3ODQ3MDM3OTQsImV4cC</t>
+          <t>{"success": true, "data": {"token": "eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJpZCI6ImNtcnN5cmk1YjAwMDBsY2I0Z2hzd2I4ZTUiLCJ1c2VybmFtZSI6ImFkbWluIiwicm9sZSI6IlNVUEVSQURNSU4iLCJpYXQiOjE3ODQ3MDQxODEsImV4cC</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         <v>401</v>
       </c>
       <c r="L3" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>200</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
         <v>200</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -872,11 +872,11 @@
         <v>201</v>
       </c>
       <c r="L7" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqk5le003xlcsgrrbkgwz6", "eventId": "cmrvqjvqm0000lcswueuniggq", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10, "createdAt":</t>
+          <t>{"success": true, "data": {"id": "cmrvqsfs3004glcsgywtg0rrx", "eventId": "cmrvqjvqm0000lcswueuniggq", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10, "createdAt":</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{"eventId": "cmrvqjvqm0000lcswueuniggq", "fullName": "Excel Tester Guest", "email": "excel.test.1784703795082@example.com", "phone": "0899999999", "company": "Excel QA Corp"}</t>
+          <t>{"eventId": "cmrvqjvqm0000lcswueuniggq", "fullName": "Excel Tester Guest", "email": "excel.test.1784704181489@example.com", "phone": "0899999999", "company": "Excel QA Corp"}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -933,11 +933,11 @@
         <v>201</v>
       </c>
       <c r="L8" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqk5nl0040lcsgl5jz45qp", "eventId": "cmrvqjvqm0000lcswueuniggq", "fullName": "Excel Tester Guest", "email": "excel.test.1784703795082@example.com", "phone": "08999</t>
+          <t>{"success": true, "data": {"id": "cmrvqsft0004jlcsgg3gxvdc3", "eventId": "cmrvqjvqm0000lcswueuniggq", "fullName": "Excel Tester Guest", "email": "excel.test.1784704181489@example.com", "phone": "08999</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"registrationId": "cmrvqk5nl0040lcsgl5jz45qp", "checkinPointId": "cmrvqk5le003xlcsgrrbkgwz6", "method": "MANUAL"}</t>
+          <t>{"registrationId": "cmrvqsft0004jlcsgg3gxvdc3", "checkinPointId": "cmrvqsfs3004glcsgywtg0rrx", "method": "MANUAL"}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -994,11 +994,11 @@
         <v>201</v>
       </c>
       <c r="L9" t="n">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"checkin": {"id": "cmrvqk5q20043lcsg0mi1ao5o", "registrationId": "cmrvqk5nl0040lcsgl5jz45qp", "checkinPointId": "cmrvqk5le003xlcsgrrbkgwz6", "checkinTime": "2026-07-22T07:03</t>
+          <t>{"success": true, "data": {"checkin": {"id": "cmrvqsftw004mlcsgkf85b5ll", "registrationId": "cmrvqsft0004jlcsgg3gxvdc3", "checkinPointId": "cmrvqsfs3004glcsgywtg0rrx", "checkinTime": "2026-07-22T07:09</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
         <v>200</v>
       </c>
       <c r="L10" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1112,11 +1112,11 @@
         <v>201</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqk5t90046lcsgtf7uoplm", "eventId": "cmrvqjvqm0000lcswueuniggq", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "status": "PENDING", "drawCount": 1, "startedAt": null, "e</t>
+          <t>{"success": true, "data": {"id": "cmrvqsfvu004plcsg88a1qlwd", "eventId": "cmrvqjvqm0000lcswueuniggq", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "status": "PENDING", "drawCount": 1, "startedAt": null, "e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>/api/draws/cmrvqk5t90046lcsgtf7uoplm/spin</t>
+          <t>/api/draws/cmrvqsfvu004plcsg88a1qlwd/spin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1173,11 +1173,11 @@
         <v>200</v>
       </c>
       <c r="L12" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"winners": [{"id": "cmrvqjvx70020lcsw64qrgb8g", "fullName": "Attendee 029", "department": "Finance", "company": "Tech Corp", "employeeType": "Contract"}], "candidates": 31}}</t>
+          <t>{"success": true, "data": {"winners": [{"id": "cmrvqjvws001ulcsw31id462s", "fullName": "Attendee 026", "department": "Engineering", "company": "Tech Corp", "employeeType": "Intern"}], "candidates": 32</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>/api/draws/winners/cmrvqk5vb0049lcsg5y5vtfki</t>
+          <t>/api/draws/winners/cmrvqsfx6004slcsg3uve7y2u</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1234,11 +1234,11 @@
         <v>200</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqk5vb0049lcsg5y5vtfki", "drawSessionId": "cmrvqk5t90046lcsgtf7uoplm", "registrationId": "cmrvqjvx70020lcsw64qrgb8g", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "stat</t>
+          <t>{"success": true, "data": {"id": "cmrvqsfx6004slcsg3uve7y2u", "drawSessionId": "cmrvqsfvu004plcsg88a1qlwd", "registrationId": "cmrvqjvws001ulcsw31id462s", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "stat</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>/api/draws/winners/cmrvqk5vb0049lcsg5y5vtfki</t>
+          <t>/api/draws/winners/cmrvqsfx6004slcsg3uve7y2u</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
         <v>200</v>
       </c>
       <c r="L14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>

--- a/tests/test_results.xlsx
+++ b/tests/test_results.xlsx
@@ -441,12 +441,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -579,11 +579,11 @@
         <v>200</v>
       </c>
       <c r="L2" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"token": "eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJpZCI6ImNtcnN5cmk1YjAwMDBsY2I0Z2hzd2I4ZTUiLCJ1c2VybmFtZSI6ImFkbWluIiwicm9sZSI6IlNVUEVSQURNSU4iLCJpYXQiOjE3ODQ3MDQxODEsImV4cC</t>
+          <t>{"success": true, "data": {"token": "eyJhbGciOiJIUzI1NiIsInR5cCI6IkpXVCJ9.eyJpZCI6ImNtcnN5cmk1YjAwMDBsY2I0Z2hzd2I4ZTUiLCJ1c2VybmFtZSI6ImFkbWluIiwicm9sZSI6IlNVUEVSQURNSU4iLCJpYXQiOjE3ODQ3MDU0NjQsImV4cC</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         <v>401</v>
       </c>
       <c r="L3" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -661,31 +661,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>List Active Events</t>
+          <t>Create New Event</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>/api/events?status=ACTIVE,PUBLISHED</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>/api/events</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>{"name": "Tech Gala Expo 1784705464585", "description": "Annual Technology Innovation Summit", "venue": "Grand Hall 1", "startDate": "2026-12-01T09:00:00.000Z", "endDate": "2026-12-01T18:00:00.000Z", "status": "ACTIVE"}</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>data.id</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -694,14 +698,14 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>{"success": true, "data": [{"id": "cmrvqjvqm0000lcswueuniggq", "name": "Tech Conference 2026", "description": "Annual technology conference with workshops, talks, and networking", "venue": "Bangkok Co</t>
+          <t>{"success": true, "data": {"id": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "Tech Gala Expo 1784705464585", "description": "Annual Technology Innovation Summit", "venue": "Grand Hall 1", "startDate": "2026-</t>
         </is>
       </c>
     </row>
@@ -718,23 +722,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Get Event Details by ID</t>
+          <t>Update Event Status to Active/Public</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>/api/events/cmrvqjvqm0000lcswueuniggq</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>/api/events/cmrvrjxu6004ylcsgyvy9qcm1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>{"status": "ACTIVE"}</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -742,7 +750,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>data.name</t>
+          <t>data.id</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -754,11 +762,11 @@
         <v>200</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqjvqm0000lcswueuniggq", "name": "Tech Conference 2026", "description": "Annual technology conference with workshops, talks, and networking", "venue": "Bangkok Con</t>
+          <t>{"success": true, "data": {"id": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "Tech Gala Expo 1784705464585", "description": "Annual Technology Innovation Summit", "venue": "Grand Hall 1", "startDate": "2026-</t>
         </is>
       </c>
     </row>
@@ -770,12 +778,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CheckinPoints</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Get Entrance Points List</t>
+          <t>Get Event Detail</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -785,7 +793,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>/api/checkin/points?eventId=cmrvqjvqm0000lcswueuniggq</t>
+          <t>/api/events/cmrvrjxu6004ylcsgyvy9qcm1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -799,7 +807,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>data.name</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -811,11 +819,11 @@
         <v>200</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>{"success": true, "data": [{"id": "cmrvqjvqu0002lcswyyqtzxlt", "eventId": "cmrvqjvqm0000lcswueuniggq", "name": "Main Entrance", "location": "Hall A - Ground Floor", "isActive": true, "sortOrder": 1, "</t>
+          <t>{"success": true, "data": {"id": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "Tech Gala Expo 1784705464585", "description": "Annual Technology Innovation Summit", "venue": "Grand Hall 1", "startDate": "2026-</t>
         </is>
       </c>
     </row>
@@ -832,35 +840,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Create New Entrance Gate</t>
+          <t>Get Entrance Points List</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>/api/checkin/points</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>{"eventId": "cmrvqjvqm0000lcswueuniggq", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10}</t>
-        </is>
-      </c>
+          <t>/api/checkin/points?eventId=cmrvrjxu6004ylcsgyvy9qcm1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>data.id</t>
+          <t>data</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -869,14 +873,14 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqsfs3004glcsgywtg0rrx", "eventId": "cmrvqjvqm0000lcswueuniggq", "name": "Excel Gate Door 1", "location": "Hall 1", "isActive": true, "sortOrder": 10, "createdAt":</t>
+          <t>{"success": true, "data": [{"id": "cmrvrjxwk0052lcsgg7502bia", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "จุดเช็กอินหลัก (Main Gate)", "location": "ทางเข้าหลัก", "isActive": true, "sortOrder": 1</t>
         </is>
       </c>
     </row>
@@ -888,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>CheckinPoints</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Register New Attendee</t>
+          <t>Create New Entrance Gate</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -903,17 +907,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>/api/registrations</t>
+          <t>/api/checkin/points</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{"eventId": "cmrvqjvqm0000lcswueuniggq", "fullName": "Excel Tester Guest", "email": "excel.test.1784704181489@example.com", "phone": "0899999999", "company": "Excel QA Corp"}</t>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "VIP Entrance Gate 1", "location": "Hall A North", "isActive": true, "sortOrder": 1}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -933,11 +937,11 @@
         <v>201</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqsft0004jlcsgg3gxvdc3", "eventId": "cmrvqjvqm0000lcswueuniggq", "fullName": "Excel Tester Guest", "email": "excel.test.1784704181489@example.com", "phone": "08999</t>
+          <t>{"success": true, "data": {"id": "cmrvrjxww0054lcsgdcdmwrc4", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "VIP Entrance Gate 1", "location": "Hall A North", "isActive": true, "sortOrder": 1, "crea</t>
         </is>
       </c>
     </row>
@@ -949,12 +953,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Checkin</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Perform Gate Check-in</t>
+          <t>Register New Attendee (Guest 1)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -964,12 +968,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>/api/checkin</t>
+          <t>/api/registrations</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>{"registrationId": "cmrvqsft0004jlcsgg3gxvdc3", "checkinPointId": "cmrvqsfs3004glcsgywtg0rrx", "method": "MANUAL"}</t>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Somchai Jaidee (Guest 1)", "email": "somchai.1784705464702@example.com", "phone": "0811111111", "company": "Tech Corp"}</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -982,7 +986,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data.checkin.id</t>
+          <t>data.id</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -994,11 +998,11 @@
         <v>201</v>
       </c>
       <c r="L9" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"checkin": {"id": "cmrvqsftw004mlcsgkf85b5ll", "registrationId": "cmrvqsft0004jlcsgg3gxvdc3", "checkinPointId": "cmrvqsfs3004glcsgywtg0rrx", "checkinTime": "2026-07-22T07:09</t>
+          <t>{"success": true, "data": {"id": "cmrvrjxxz0057lcsgyoys2n02", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Somchai Jaidee (Guest 1)", "email": "somchai.1784705464702@example.com", "phone": "08</t>
         </is>
       </c>
     </row>
@@ -1010,36 +1014,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LuckyDraw</t>
+          <t>Checkin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fetch Prizes &amp; Eligible Count</t>
+          <t>Perform Gate Check-in (Guest 1)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>/api/prizes?eventId=cmrvqjvqm0000lcswueuniggq</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>/api/checkin</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>{"registrationId": "cmrvrjxxz0057lcsgyoys2n02", "checkinPointId": "cmrvrjxww0054lcsgdcdmwrc4", "method": "MANUAL"}</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>data.checkin.id</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1048,14 +1056,14 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L10" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>{"success": true, "data": [{"id": "cmrvqjvrn000alcsw216ijgbl", "eventId": "cmrvqjvqm0000lcswueuniggq", "name": "MacBook Pro 16\"", "description": "Apple MacBook Pro 16-inch M4 Pro", "image": null, "qu</t>
+          <t>{"success": true, "data": {"checkin": {"id": "cmrvrjxz2005alcsgc8dsu6js", "registrationId": "cmrvrjxxz0057lcsgyoys2n02", "checkinPointId": "cmrvrjxww0054lcsgdcdmwrc4", "checkinTime": "2026-07-22T07:31</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1075,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LuckyDraw</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Start Draw Session</t>
+          <t>Register New Attendee (Guest 2)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1082,17 +1090,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>/api/draws/start</t>
+          <t>/api/registrations</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>{"eventId": "cmrvqjvqm0000lcswueuniggq", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "drawCount": 1}</t>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Siriporn Boonmee (Guest 2)", "email": "siriporn.1784705464813@example.com", "phone": "0822222222", "company": "Innovate Ltd"}</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1112,11 +1120,11 @@
         <v>201</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqsfvu004plcsg88a1qlwd", "eventId": "cmrvqjvqm0000lcswueuniggq", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "status": "PENDING", "drawCount": 1, "startedAt": null, "e</t>
+          <t xml:space="preserve">{"success": true, "data": {"id": "cmrvrjy0y005dlcsge0g3uten", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Siriporn Boonmee (Guest 2)", "email": "siriporn.1784705464813@example.com", "phone": </t>
         </is>
       </c>
     </row>
@@ -1128,12 +1136,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LuckyDraw</t>
+          <t>Checkin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Execute Spin Fisher-Yates Draw</t>
+          <t>Perform Gate Check-in (Guest 2)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1143,12 +1151,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>/api/draws/cmrvqsfvu004plcsg88a1qlwd/spin</t>
+          <t>/api/checkin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>{"count": 1}</t>
+          <t>{"registrationId": "cmrvrjy0y005dlcsge0g3uten", "checkinPointId": "cmrvrjxww0054lcsgdcdmwrc4", "method": "MANUAL"}</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1157,11 +1165,11 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data.winners</t>
+          <t>data.checkin.id</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1170,14 +1178,14 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"winners": [{"id": "cmrvqjvws001ulcsw31id462s", "fullName": "Attendee 026", "department": "Engineering", "company": "Tech Corp", "employeeType": "Intern"}], "candidates": 32</t>
+          <t>{"success": true, "data": {"checkin": {"id": "cmrvrjy1y005glcsgk8868dmg", "registrationId": "cmrvrjy0y005dlcsge0g3uten", "checkinPointId": "cmrvrjxww0054lcsgdcdmwrc4", "checkinTime": "2026-07-22T07:31</t>
         </is>
       </c>
     </row>
@@ -1189,40 +1197,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WinnerMgmt</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Update Winner Status to ACCEPTED</t>
+          <t>Register New Attendee (Guest 3)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>/api/draws/winners/cmrvqsfx6004slcsg3uve7y2u</t>
+          <t>/api/registrations</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>{"status": "ACCEPTED"}</t>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Wichai Chaichana (Guest 3)", "email": "wichai.1784705464892@example.com", "phone": "0833333333", "company": "Digital Group"}</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data.status</t>
+          <t>data.id</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1231,14 +1239,14 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L13" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>{"success": true, "data": {"id": "cmrvqsfx6004slcsg3uve7y2u", "drawSessionId": "cmrvqsfvu004plcsg88a1qlwd", "registrationId": "cmrvqjvws001ulcsw31id462s", "prizeId": "cmrvqjvrn000alcsw216ijgbl", "stat</t>
+          <t>{"success": true, "data": {"id": "cmrvrjy32005jlcsg8gg7grze", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Wichai Chaichana (Guest 3)", "email": "wichai.1784705464892@example.com", "phone": "0</t>
         </is>
       </c>
     </row>
@@ -1250,50 +1258,1449 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Checkin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Perform Gate Check-in (Guest 3)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>/api/checkin</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>{"registrationId": "cmrvrjy32005jlcsg8gg7grze", "checkinPointId": "cmrvrjxww0054lcsgdcdmwrc4", "method": "MANUAL"}</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>201</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>data.checkin.id</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>201</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"checkin": {"id": "cmrvrjy3s005mlcsglwgtv0ol", "registrationId": "cmrvrjy32005jlcsg8gg7grze", "checkinPointId": "cmrvrjxww0054lcsgdcdmwrc4", "checkinTime": "2026-07-22T07:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 4)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Anan Srisuk (Guest 4)", "email": "anan.1784705464959@example.com", "phone": "0844444444", "company": "Software Inc"}</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>201</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>201</v>
+      </c>
+      <c r="L15" t="n">
+        <v>33</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjy4v005plcsg93ysbx41", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Anan Srisuk (Guest 4)", "email": "anan.1784705464959@example.com", "phone": "08444444</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Checkin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Perform Gate Check-in (Guest 4)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>/api/checkin</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>{"registrationId": "cmrvrjy4v005plcsg93ysbx41", "checkinPointId": "cmrvrjxww0054lcsgdcdmwrc4", "method": "MANUAL"}</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>201</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>data.checkin.id</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>201</v>
+      </c>
+      <c r="L16" t="n">
+        <v>31</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"checkin": {"id": "cmrvrjy5m005slcsgy0np5pk0", "registrationId": "cmrvrjy4v005plcsg93ysbx41", "checkinPointId": "cmrvrjxww0054lcsgdcdmwrc4", "checkinTime": "2026-07-22T07:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 5)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Kanya Wattana (Guest 5)", "email": "kanya.1784705465024@example.com", "phone": "0855555555", "company": "Cloud Systems"}</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>201</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>201</v>
+      </c>
+      <c r="L17" t="n">
+        <v>29</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjy6o005vlcsgm451mfcg", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Kanya Wattana (Guest 5)", "email": "kanya.1784705465024@example.com", "phone": "08555</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 6)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Nattapong Somboon (Guest 6)", "email": "nattapong.1784705465054@example.com", "phone": "0866666666", "company": "Cyber Security"}</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>201</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>201</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjy7k005ylcsgbs5zj76q", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Nattapong Somboon (Guest 6)", "email": "nattapong.1784705465054@example.com", "phone"</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 7)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Piyada Rattanaporn (Guest 7)", "email": "piyada.1784705465089@example.com", "phone": "0877777777", "company": "Data Analytics"}</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>201</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>201</v>
+      </c>
+      <c r="L19" t="n">
+        <v>32</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"success": true, "data": {"id": "cmrvrjy8l0061lcsgyijdd8lf", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Piyada Rattanaporn (Guest 7)", "email": "piyada.1784705465089@example.com", "phone": </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 8)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Thanakorn Prasert (Guest 8)", "email": "thanakorn.1784705465122@example.com", "phone": "0888888888", "company": "AI Labs"}</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>201</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>201</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjy9f0064lcsg3h0ml5tk", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Thanakorn Prasert (Guest 8)", "email": "thanakorn.1784705465122@example.com", "phone"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 9)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Chutima Wongwian (Guest 9)", "email": "chutima.1784705465152@example.com", "phone": "0899999991", "company": "Media Network"}</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>201</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>201</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjyaa0067lcsgsvtg8eyx", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Chutima Wongwian (Guest 9)", "email": "chutima.1784705465152@example.com", "phone": "</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 10)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Phopkrit Panich (Guest 10)", "email": "phopkrit.1784705465184@example.com", "phone": "0899999992", "company": "Finance Hub"}</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>201</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>201</v>
+      </c>
+      <c r="L22" t="n">
+        <v>29</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"success": true, "data": {"id": "cmrvrjyb3006alcsgaq81ryjv", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Phopkrit Panich (Guest 10)", "email": "phopkrit.1784705465184@example.com", "phone": </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 11)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Suthep Ruangrit (Guest 11)", "email": "suthep.1784705465213@example.com", "phone": "0899999993", "company": "Logistics Pro"}</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>201</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>201</v>
+      </c>
+      <c r="L23" t="n">
+        <v>27</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjybx006dlcsg57cqt8pn", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Suthep Ruangrit (Guest 11)", "email": "suthep.1784705465213@example.com", "phone": "0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 12)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Rungtiwa Kaewmanee (Guest 12)", "email": "rungtiwa.1784705465242@example.com", "phone": "0899999994", "company": "Creative Studio"}</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>201</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>201</v>
+      </c>
+      <c r="L24" t="n">
+        <v>26</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjyco006glcsga46pr63b", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Rungtiwa Kaewmanee (Guest 12)", "email": "rungtiwa.1784705465242@example.com", "phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 13)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Banthit Charoen (Guest 13)", "email": "banthit.1784705465268@example.com", "phone": "0899999995", "company": "Mobile Apps"}</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>201</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>201</v>
+      </c>
+      <c r="L25" t="n">
+        <v>27</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjydf006jlcsgor86kgqp", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Banthit Charoen (Guest 13)", "email": "banthit.1784705465268@example.com", "phone": "</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 14)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Wanida Saetang (Guest 14)", "email": "wanida.1784705465296@example.com", "phone": "0899999996", "company": "E-Commerce Group"}</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>201</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>201</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjye8006mlcsg0gofpg9g", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Wanida Saetang (Guest 14)", "email": "wanida.1784705465296@example.com", "phone": "08</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 15)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Kraisorn Decha (Guest 15)", "email": "kraisorn.1784705465328@example.com", "phone": "0899999997", "company": "Robotics Corp"}</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>201</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>201</v>
+      </c>
+      <c r="L27" t="n">
+        <v>27</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjyf5006plcsg3e3053nf", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Kraisorn Decha (Guest 15)", "email": "kraisorn.1784705465328@example.com", "phone": "</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 16)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Worawat Songsak (Guest 16)", "email": "worawat.1784705465359@example.com", "phone": "0899999998", "company": "Gaming World"}</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>201</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>201</v>
+      </c>
+      <c r="L28" t="n">
+        <v>23</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjyfx006slcsgusfc9pqa", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Worawat Songsak (Guest 16)", "email": "worawat.1784705465359@example.com", "phone": "</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 17)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Jintana Phusit (Guest 17)", "email": "jintana.1784705465386@example.com", "phone": "0812345601", "company": "Health Tech"}</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>201</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>201</v>
+      </c>
+      <c r="L29" t="n">
+        <v>28</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjygp006vlcsgbbv0fbq1", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Jintana Phusit (Guest 17)", "email": "jintana.1784705465386@example.com", "phone": "0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 18)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Prasit Manop (Guest 18)", "email": "prasit.1784705465416@example.com", "phone": "0812345602", "company": "Green Energy"}</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>201</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>201</v>
+      </c>
+      <c r="L30" t="n">
+        <v>30</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjyho006ylcsggd13p2rr", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Prasit Manop (Guest 18)", "email": "prasit.1784705465416@example.com", "phone": "0812</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Register New Attendee (Guest 19)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>/api/registrations</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Rattana Chokdee (Guest 19)", "email": "rattana.1784705465452@example.com", "phone": "0812345603", "company": "Smart City"}</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>201</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>201</v>
+      </c>
+      <c r="L31" t="n">
+        <v>26</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjyij0071lcsgm5b86dn6", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "fullName": "Rattana Chokdee (Guest 19)", "email": "rattana.1784705465452@example.com", "phone": "</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Prizes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Create Prize for Event</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>/api/prizes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "Grand Prize iPhone 16 Pro", "description": "Top Lucky Draw Prize", "quantity": 5, "sortOrder": 1}</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>201</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>201</v>
+      </c>
+      <c r="L32" t="n">
+        <v>13</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjyj00074lcsgv38ur5fk", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "Grand Prize iPhone 16 Pro", "description": "Top Lucky Draw Prize", "image": null, "quanti</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LuckyDraw</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fetch Prizes &amp; Eligible Count</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>/api/prizes?eventId=cmrvrjxu6004ylcsgyvy9qcm1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>200</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>200</v>
+      </c>
+      <c r="L33" t="n">
+        <v>19</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": [{"id": "cmrvrjyj00074lcsgv38ur5fk", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "name": "Grand Prize iPhone 16 Pro", "description": "Top Lucky Draw Prize", "image": null, "quant</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LuckyDraw</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Start Lucky Draw Session</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>/api/draws/start</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>{"eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "prizeId": "cmrvrjyj00074lcsgv38ur5fk", "drawCount": 1}</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>201</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>data.id</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>201</v>
+      </c>
+      <c r="L34" t="n">
+        <v>25</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjyk30077lcsgs1xclz81", "eventId": "cmrvrjxu6004ylcsgyvy9qcm1", "prizeId": "cmrvrjyj00074lcsgv38ur5fk", "status": "PENDING", "drawCount": 1, "startedAt": null, "e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LuckyDraw</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Execute Fisher-Yates Spin Draw (1 Winner)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>/api/draws/cmrvrjyk30077lcsgs1xclz81/spin</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>{"count": 1}</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>200</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>data.winners</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>200</v>
+      </c>
+      <c r="L35" t="n">
+        <v>66</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"success": true, "data": {"winners": [{"id": "cmrvrjy6o005vlcsgm451mfcg", "fullName": "Kanya Wattana (Guest 5)", "department": null, "company": "Cloud Systems", "employeeType": null}], "candidates": </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>WinnerMgmt</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Update Winner Status to ACCEPTED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>/api/draws/winners/cmrvrjylj007alcsgy93ixu2u</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>{"status": "ACCEPTED"}</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>200</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>data.status</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>200</v>
+      </c>
+      <c r="L36" t="n">
+        <v>24</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>{"success": true, "data": {"id": "cmrvrjylj007alcsgy93ixu2u", "drawSessionId": "cmrvrjyk30077lcsgs1xclz81", "registrationId": "cmrvrjy6o005vlcsgm451mfcg", "prizeId": "cmrvrjyj00074lcsgv38ur5fk", "stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>WinnerMgmt</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Delete Winner &amp; Recalculate Quota</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>/api/draws/winners/cmrvqsfx6004slcsg3uve7y2u</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>/api/draws/winners/cmrvrjylj007alcsgy93ixu2u</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H37" t="n">
         <v>200</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>200</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L37" t="n">
         <v>22</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>{"success": true, "message": "Winner deleted successfully"}</t>
         </is>
